--- a/data/source-workbooks/driver_templates_expanded_untruncated.xlsx
+++ b/data/source-workbooks/driver_templates_expanded_untruncated.xlsx
@@ -1260,17 +1260,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H2" t="n">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OH1668243</t>
+          <t>OH0000075</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="U2" s="2" t="n">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>jcarter@yahoo.com</t>
+          <t>jcarter@example.com</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1240 W 6th St</t>
+          <t>220 Demo Street</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="BF2" s="2" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>OH1668243</t>
+          <t>OH0000075</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>(614) 821-5212</t>
+          <t>(614) 555-0107</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1790,17 +1790,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H3" t="n">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OH2933152</t>
+          <t>OH0000092</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>jcarter@yahoo.com</t>
+          <t>jcarter@example.com</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1240 W 6th St</t>
+          <t>220 Demo Street</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="BF3" s="2" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>OH1668244</t>
+          <t>OH0000076</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>(614) 821-5212</t>
+          <t>(614) 555-0107</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -2320,17 +2320,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H4" t="n">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>OH6381314</t>
+          <t>OH0000111</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>jcarter@yahoo.com</t>
+          <t>jcarter@example.com</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1240 W 6th St</t>
+          <t>220 Demo Street</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="BF4" s="2" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>OH1668245</t>
+          <t>OH0000077</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>(614) 821-5212</t>
+          <t>(614) 555-0107</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H5" t="n">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OH8275310</t>
+          <t>OH0000127</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="U5" s="2" t="n">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>jcarter@yahoo.com</t>
+          <t>jcarter@example.com</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1240 W 6th St</t>
+          <t>220 Demo Street</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="BF5" s="2" t="n">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>OH1668246</t>
+          <t>OH0000078</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>(614) 821-5212</t>
+          <t>(614) 555-0107</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H6" t="n">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OH8643525</t>
+          <t>OH0000137</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="U6" s="2" t="n">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>jcarter@yahoo.com</t>
+          <t>jcarter@example.com</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1240 W 6th St</t>
+          <t>220 Demo Street</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="BF6" s="2" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>OH1668247</t>
+          <t>OH0000079</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>(614) 821-5212</t>
+          <t>(614) 555-0107</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H7" t="n">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OH8694835</t>
+          <t>OH0000138</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="U7" s="2" t="n">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>jcarter@yahoo.com</t>
+          <t>jcarter@example.com</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1240 W 6th St</t>
+          <t>220 Demo Street</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="BF7" s="2" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>OH1668248</t>
+          <t>OH0000080</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>(614) 821-5212</t>
+          <t>(614) 555-0107</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -4445,17 +4445,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H8" t="n">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OH7359899</t>
+          <t>OH0000124</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="U8" s="2" t="n">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -4531,12 +4531,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>jcarter@yahoo.com</t>
+          <t>jcarter@example.com</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1240 W 6th St</t>
+          <t>220 Demo Street</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>***-**-9443</t>
+          <t>***-**-0123</t>
         </is>
       </c>
       <c r="BF8" s="2" t="n">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>OH1668249</t>
+          <t>OH0000081</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>(614) 821-5212</t>
+          <t>(614) 555-0107</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4975,17 +4975,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H9" t="n">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>IL3091126</t>
+          <t>IL0000041</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="U9" s="2" t="n">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>marialopez@aol.com</t>
+          <t>marialopez@example.com</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave</t>
+          <t>770 Demo Street</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="BF9" s="2" t="n">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>IL3091126</t>
+          <t>IL0000041</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>(312) 284-7914</t>
+          <t>(312) 555-0101</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H10" t="n">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>IL9530000</t>
+          <t>IL0000068</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="U10" s="2" t="n">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>marialopez@aol.com</t>
+          <t>marialopez@example.com</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave</t>
+          <t>770 Demo Street</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="BF10" s="2" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>IL3091127</t>
+          <t>IL0000042</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>(312) 284-7914</t>
+          <t>(312) 555-0101</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H11" t="n">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>IL3900948</t>
+          <t>IL0000056</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="U11" s="2" t="n">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>marialopez@aol.com</t>
+          <t>marialopez@example.com</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave</t>
+          <t>770 Demo Street</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="BF11" s="2" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>IL3091128</t>
+          <t>IL0000043</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>(312) 284-7914</t>
+          <t>(312) 555-0101</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -6625,17 +6625,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H12" t="n">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>IL6663817</t>
+          <t>IL0000065</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="U12" s="2" t="n">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -6711,12 +6711,12 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>marialopez@aol.com</t>
+          <t>marialopez@example.com</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave</t>
+          <t>770 Demo Street</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="BF12" s="2" t="n">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>IL3091129</t>
+          <t>IL0000044</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>(312) 284-7914</t>
+          <t>(312) 555-0101</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
@@ -7175,17 +7175,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7194,10 +7194,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H13" t="n">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>IL9293900</t>
+          <t>IL0000067</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="U13" s="2" t="n">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>marialopez@aol.com</t>
+          <t>marialopez@example.com</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave</t>
+          <t>770 Demo Street</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="BF13" s="2" t="n">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>IL3091130</t>
+          <t>IL0000045</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>(312) 284-7914</t>
+          <t>(312) 555-0101</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H14" t="n">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>IL4346440</t>
+          <t>IL0000058</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="U14" s="2" t="n">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -7816,12 +7816,12 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>marialopez@aol.com</t>
+          <t>marialopez@example.com</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave</t>
+          <t>770 Demo Street</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="BF14" s="2" t="n">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>IL3091131</t>
+          <t>IL0000046</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>(312) 284-7914</t>
+          <t>(312) 555-0101</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
@@ -8280,17 +8280,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H15" t="n">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>IL4913140</t>
+          <t>IL0000061</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="U15" s="2" t="n">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>marialopez@aol.com</t>
+          <t>marialopez@example.com</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave</t>
+          <t>770 Demo Street</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>***-**-3407</t>
+          <t>***-**-0105</t>
         </is>
       </c>
       <c r="BF15" s="2" t="n">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>IL3091132</t>
+          <t>IL0000047</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>(312) 284-7914</t>
+          <t>(312) 555-0101</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H16" t="n">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>GA7446431</t>
+          <t>GA0000013</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="U16" s="2" t="n">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>alexkim@gmail.com</t>
+          <t>alexkim@example.com</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>780 Peachtree St</t>
+          <t>960 Demo Street</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="BF16" s="2" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>GA7446431</t>
+          <t>GA0000013</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>(404) 720-5860</t>
+          <t>(404) 555-0107</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H17" t="n">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>GA3549920</t>
+          <t>GA0000006</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="U17" s="2" t="n">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9451,12 +9451,12 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>alexkim@gmail.com</t>
+          <t>alexkim@example.com</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>780 Peachtree St</t>
+          <t>960 Demo Street</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="BF17" s="2" t="n">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>GA7446432</t>
+          <t>GA0000014</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>(404) 720-5860</t>
+          <t>(404) 555-0107</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
@@ -9900,17 +9900,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -9919,10 +9919,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H18" t="n">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>GA5957495</t>
+          <t>GA0000011</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="U18" s="2" t="n">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -9986,12 +9986,12 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>alexkim@gmail.com</t>
+          <t>alexkim@example.com</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>780 Peachtree St</t>
+          <t>960 Demo Street</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="BF18" s="2" t="n">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>GA7446433</t>
+          <t>GA0000015</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>(404) 720-5860</t>
+          <t>(404) 555-0107</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
@@ -10435,17 +10435,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H19" t="n">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>GA3499514</t>
+          <t>GA0000005</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="U19" s="2" t="n">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -10521,12 +10521,12 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>alexkim@gmail.com</t>
+          <t>alexkim@example.com</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>780 Peachtree St</t>
+          <t>960 Demo Street</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="BF19" s="2" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>GA7446434</t>
+          <t>GA0000016</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>(404) 720-5860</t>
+          <t>(404) 555-0107</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
@@ -10970,17 +10970,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H20" t="n">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>GA3381500</t>
+          <t>GA0000004</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -11042,7 +11042,7 @@
         </is>
       </c>
       <c r="U20" s="2" t="n">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -11056,12 +11056,12 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>alexkim@gmail.com</t>
+          <t>alexkim@example.com</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>780 Peachtree St</t>
+          <t>960 Demo Street</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="BF20" s="2" t="n">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>GA7446435</t>
+          <t>GA0000017</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>(404) 720-5860</t>
+          <t>(404) 555-0107</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
@@ -11505,17 +11505,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11524,10 +11524,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H21" t="n">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>GA8768417</t>
+          <t>GA0000027</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="U21" s="2" t="n">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -11596,12 +11596,12 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>alexkim@gmail.com</t>
+          <t>alexkim@example.com</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>780 Peachtree St</t>
+          <t>960 Demo Street</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="BF21" s="2" t="n">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>GA7446436</t>
+          <t>GA0000018</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>(404) 720-5860</t>
+          <t>(404) 555-0107</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
@@ -12045,17 +12045,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -12064,10 +12064,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H22" t="n">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>GA1828575</t>
+          <t>GA0000002</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -12117,7 +12117,7 @@
         </is>
       </c>
       <c r="U22" s="2" t="n">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -12131,12 +12131,12 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>alexkim@gmail.com</t>
+          <t>alexkim@example.com</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>780 Peachtree St</t>
+          <t>960 Demo Street</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>***-**-7047</t>
+          <t>***-**-0116</t>
         </is>
       </c>
       <c r="BF22" s="2" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>GA7446437</t>
+          <t>GA0000019</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>(404) 720-5860</t>
+          <t>(404) 555-0107</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
@@ -12580,17 +12580,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -12599,10 +12599,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H23" t="n">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>OH8493496</t>
+          <t>OH0000130</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="U23" s="2" t="n">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>priyapatel@yahoo.com</t>
+          <t>priyapatel@example.com</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2200 Superior Ave</t>
+          <t>520 Demo Street</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="BF23" s="2" t="n">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>OH8493496</t>
+          <t>OH0000130</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>(614) 897-8705</t>
+          <t>(614) 555-0111</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
@@ -13125,17 +13125,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13144,10 +13144,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H24" t="n">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>OH4694295</t>
+          <t>OH0000099</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="U24" s="2" t="n">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -13211,12 +13211,12 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>priyapatel@yahoo.com</t>
+          <t>priyapatel@example.com</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2200 Superior Ave</t>
+          <t>520 Demo Street</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="BF24" s="2" t="n">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>OH8493497</t>
+          <t>OH0000131</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>(614) 897-8705</t>
+          <t>(614) 555-0111</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
@@ -13670,17 +13670,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13689,10 +13689,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H25" t="n">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>OH7280038</t>
+          <t>OH0000123</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
@@ -13742,7 +13742,7 @@
         </is>
       </c>
       <c r="U25" s="2" t="n">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -13756,12 +13756,12 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>priyapatel@yahoo.com</t>
+          <t>priyapatel@example.com</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2200 Superior Ave</t>
+          <t>520 Demo Street</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="BF25" s="2" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>OH8493498</t>
+          <t>OH0000132</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>(614) 897-8705</t>
+          <t>(614) 555-0111</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
@@ -14215,17 +14215,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H26" t="n">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>OH9775880</t>
+          <t>OH0000149</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -14287,7 +14287,7 @@
         </is>
       </c>
       <c r="U26" s="2" t="n">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -14301,12 +14301,12 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>priyapatel@yahoo.com</t>
+          <t>priyapatel@example.com</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2200 Superior Ave</t>
+          <t>520 Demo Street</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="BF26" s="2" t="n">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>OH8493499</t>
+          <t>OH0000133</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>(614) 897-8705</t>
+          <t>(614) 555-0111</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -14779,10 +14779,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H27" t="n">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>OH1046362</t>
+          <t>OH0000072</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -14832,7 +14832,7 @@
         </is>
       </c>
       <c r="U27" s="2" t="n">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -14846,12 +14846,12 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>priyapatel@yahoo.com</t>
+          <t>priyapatel@example.com</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2200 Superior Ave</t>
+          <t>520 Demo Street</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="BF27" s="2" t="n">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>OH8493500</t>
+          <t>OH0000134</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>(614) 897-8705</t>
+          <t>(614) 555-0111</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
@@ -15305,17 +15305,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -15324,10 +15324,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H28" t="n">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>OH1138650</t>
+          <t>OH0000074</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -15382,7 +15382,7 @@
         </is>
       </c>
       <c r="U28" s="2" t="n">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>priyapatel@yahoo.com</t>
+          <t>priyapatel@example.com</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2200 Superior Ave</t>
+          <t>520 Demo Street</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="BF28" s="2" t="n">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>OH8493501</t>
+          <t>OH0000135</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>(614) 897-8705</t>
+          <t>(614) 555-0111</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
@@ -15855,17 +15855,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -15874,10 +15874,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H29" t="n">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>OH4059570</t>
+          <t>OH0000095</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -15927,7 +15927,7 @@
         </is>
       </c>
       <c r="U29" s="2" t="n">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -15941,12 +15941,12 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>priyapatel@yahoo.com</t>
+          <t>priyapatel@example.com</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2200 Superior Ave</t>
+          <t>520 Demo Street</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -16065,7 +16065,7 @@
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>***-**-8257</t>
+          <t>***-**-0119</t>
         </is>
       </c>
       <c r="BF29" s="2" t="n">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>OH8493502</t>
+          <t>OH0000136</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>(614) 897-8705</t>
+          <t>(614) 555-0111</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
@@ -16400,17 +16400,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -16419,10 +16419,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H30" t="n">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>OH2779041</t>
+          <t>OH0000084</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -16472,7 +16472,7 @@
         </is>
       </c>
       <c r="U30" s="2" t="n">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -16486,12 +16486,12 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>ktanaka@yahoo.com</t>
+          <t>ktanaka@example.com</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>115 E Broad St</t>
+          <t>150 Demo Street</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="BF30" s="2" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>OH2779041</t>
+          <t>OH0000084</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>(614) 806-7535</t>
+          <t>(614) 555-0106</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
@@ -16950,17 +16950,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -16969,10 +16969,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H31" t="n">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>OH3434069</t>
+          <t>OH0000093</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -17022,7 +17022,7 @@
         </is>
       </c>
       <c r="U31" s="2" t="n">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -17036,12 +17036,12 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>ktanaka@yahoo.com</t>
+          <t>ktanaka@example.com</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>115 E Broad St</t>
+          <t>150 Demo Street</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="BF31" s="2" t="n">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>OH2779042</t>
+          <t>OH0000085</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>(614) 806-7535</t>
+          <t>(614) 555-0106</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
@@ -17500,17 +17500,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -17519,10 +17519,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H32" t="n">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>OH6720716</t>
+          <t>OH0000119</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="U32" s="2" t="n">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -17586,12 +17586,12 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>ktanaka@yahoo.com</t>
+          <t>ktanaka@example.com</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>115 E Broad St</t>
+          <t>150 Demo Street</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="BF32" s="2" t="n">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="CL32" t="inlineStr">
         <is>
-          <t>OH2779043</t>
+          <t>OH0000086</t>
         </is>
       </c>
       <c r="CM32" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="CR32" t="inlineStr">
         <is>
-          <t>(614) 806-7535</t>
+          <t>(614) 555-0106</t>
         </is>
       </c>
       <c r="CS32" t="inlineStr">
@@ -18050,17 +18050,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -18069,10 +18069,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H33" t="n">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>OH5640312</t>
+          <t>OH0000102</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -18122,7 +18122,7 @@
         </is>
       </c>
       <c r="U33" s="2" t="n">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -18136,12 +18136,12 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>ktanaka@yahoo.com</t>
+          <t>ktanaka@example.com</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>115 E Broad St</t>
+          <t>150 Demo Street</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="BF33" s="2" t="n">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="CL33" t="inlineStr">
         <is>
-          <t>OH2779044</t>
+          <t>OH0000087</t>
         </is>
       </c>
       <c r="CM33" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="CR33" t="inlineStr">
         <is>
-          <t>(614) 806-7535</t>
+          <t>(614) 555-0106</t>
         </is>
       </c>
       <c r="CS33" t="inlineStr">
@@ -18600,17 +18600,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -18619,10 +18619,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H34" t="n">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>OH7627072</t>
+          <t>OH0000125</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -18672,7 +18672,7 @@
         </is>
       </c>
       <c r="U34" s="2" t="n">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -18686,12 +18686,12 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>ktanaka@yahoo.com</t>
+          <t>ktanaka@example.com</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>115 E Broad St</t>
+          <t>150 Demo Street</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="BF34" s="2" t="n">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="CL34" t="inlineStr">
         <is>
-          <t>OH2779045</t>
+          <t>OH0000088</t>
         </is>
       </c>
       <c r="CM34" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="CR34" t="inlineStr">
         <is>
-          <t>(614) 806-7535</t>
+          <t>(614) 555-0106</t>
         </is>
       </c>
       <c r="CS34" t="inlineStr">
@@ -19150,17 +19150,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -19169,10 +19169,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H35" t="n">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>OH1919210</t>
+          <t>OH0000082</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
@@ -19227,7 +19227,7 @@
         </is>
       </c>
       <c r="U35" s="2" t="n">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -19241,12 +19241,12 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>ktanaka@yahoo.com</t>
+          <t>ktanaka@example.com</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>115 E Broad St</t>
+          <t>150 Demo Street</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="BF35" s="2" t="n">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="CL35" t="inlineStr">
         <is>
-          <t>OH2779046</t>
+          <t>OH0000089</t>
         </is>
       </c>
       <c r="CM35" t="inlineStr">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="CR35" t="inlineStr">
         <is>
-          <t>(614) 806-7535</t>
+          <t>(614) 555-0106</t>
         </is>
       </c>
       <c r="CS35" t="inlineStr">
@@ -19705,17 +19705,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -19724,10 +19724,10 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H36" t="n">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>OH7765263</t>
+          <t>OH0000126</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -19777,7 +19777,7 @@
         </is>
       </c>
       <c r="U36" s="2" t="n">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -19791,12 +19791,12 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>ktanaka@yahoo.com</t>
+          <t>ktanaka@example.com</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>115 E Broad St</t>
+          <t>150 Demo Street</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>***-**-1789</t>
+          <t>***-**-0102</t>
         </is>
       </c>
       <c r="BF36" s="2" t="n">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="CL36" t="inlineStr">
         <is>
-          <t>OH2779047</t>
+          <t>OH0000090</t>
         </is>
       </c>
       <c r="CM36" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="CR36" t="inlineStr">
         <is>
-          <t>(614) 806-7535</t>
+          <t>(614) 555-0106</t>
         </is>
       </c>
       <c r="CS36" t="inlineStr">
@@ -20255,17 +20255,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -20274,10 +20274,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H37" t="n">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>TX3261112</t>
+          <t>TX0000158</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="U37" s="2" t="n">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -20341,12 +20341,12 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>mchen@hotmail.com</t>
+          <t>mchen@example.com</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>500 Pacific Ave</t>
+          <t>810 Demo Street</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="BF37" s="2" t="n">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="CL37" t="inlineStr">
         <is>
-          <t>TX3261112</t>
+          <t>TX0000158</t>
         </is>
       </c>
       <c r="CM37" t="inlineStr">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="CR37" t="inlineStr">
         <is>
-          <t>(512) 621-2178</t>
+          <t>(512) 555-0100</t>
         </is>
       </c>
       <c r="CS37" t="inlineStr">
@@ -20790,17 +20790,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -20809,10 +20809,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H38" t="n">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>TX3531641</t>
+          <t>TX0000165</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -20862,7 +20862,7 @@
         </is>
       </c>
       <c r="U38" s="2" t="n">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -20876,12 +20876,12 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>mchen@hotmail.com</t>
+          <t>mchen@example.com</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>500 Pacific Ave</t>
+          <t>810 Demo Street</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="BF38" s="2" t="n">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="CL38" t="inlineStr">
         <is>
-          <t>TX3261113</t>
+          <t>TX0000159</t>
         </is>
       </c>
       <c r="CM38" t="inlineStr">
@@ -21143,7 +21143,7 @@
       </c>
       <c r="CR38" t="inlineStr">
         <is>
-          <t>(512) 621-2178</t>
+          <t>(512) 555-0100</t>
         </is>
       </c>
       <c r="CS38" t="inlineStr">
@@ -21325,17 +21325,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -21344,10 +21344,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H39" t="n">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>TX2647879</t>
+          <t>TX0000155</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -21397,7 +21397,7 @@
         </is>
       </c>
       <c r="U39" s="2" t="n">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -21411,12 +21411,12 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>mchen@hotmail.com</t>
+          <t>mchen@example.com</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>500 Pacific Ave</t>
+          <t>810 Demo Street</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="BF39" s="2" t="n">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="CL39" t="inlineStr">
         <is>
-          <t>TX3261114</t>
+          <t>TX0000160</t>
         </is>
       </c>
       <c r="CM39" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="CR39" t="inlineStr">
         <is>
-          <t>(512) 621-2178</t>
+          <t>(512) 555-0100</t>
         </is>
       </c>
       <c r="CS39" t="inlineStr">
@@ -21860,17 +21860,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -21879,10 +21879,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H40" t="n">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>TX3779357</t>
+          <t>TX0000166</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -21932,7 +21932,7 @@
         </is>
       </c>
       <c r="U40" s="2" t="n">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -21946,12 +21946,12 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>mchen@hotmail.com</t>
+          <t>mchen@example.com</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>500 Pacific Ave</t>
+          <t>810 Demo Street</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="BF40" s="2" t="n">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="CL40" t="inlineStr">
         <is>
-          <t>TX3261115</t>
+          <t>TX0000161</t>
         </is>
       </c>
       <c r="CM40" t="inlineStr">
@@ -22213,7 +22213,7 @@
       </c>
       <c r="CR40" t="inlineStr">
         <is>
-          <t>(512) 621-2178</t>
+          <t>(512) 555-0100</t>
         </is>
       </c>
       <c r="CS40" t="inlineStr">
@@ -22395,17 +22395,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -22414,10 +22414,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H41" t="n">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>TX3175879</t>
+          <t>TX0000156</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -22467,7 +22467,7 @@
         </is>
       </c>
       <c r="U41" s="2" t="n">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>mchen@hotmail.com</t>
+          <t>mchen@example.com</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>500 Pacific Ave</t>
+          <t>810 Demo Street</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="BF41" s="2" t="n">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="CL41" t="inlineStr">
         <is>
-          <t>TX3261116</t>
+          <t>TX0000162</t>
         </is>
       </c>
       <c r="CM41" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="CR41" t="inlineStr">
         <is>
-          <t>(512) 621-2178</t>
+          <t>(512) 555-0100</t>
         </is>
       </c>
       <c r="CS41" t="inlineStr">
@@ -22930,17 +22930,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -22949,10 +22949,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H42" t="n">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>TX8659153</t>
+          <t>TX0000167</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="U42" s="2" t="n">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>mchen@hotmail.com</t>
+          <t>mchen@example.com</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>500 Pacific Ave</t>
+          <t>810 Demo Street</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -23135,7 +23135,7 @@
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="BF42" s="2" t="n">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="CL42" t="inlineStr">
         <is>
-          <t>TX3261117</t>
+          <t>TX0000163</t>
         </is>
       </c>
       <c r="CM42" t="inlineStr">
@@ -23288,7 +23288,7 @@
       </c>
       <c r="CR42" t="inlineStr">
         <is>
-          <t>(512) 621-2178</t>
+          <t>(512) 555-0100</t>
         </is>
       </c>
       <c r="CS42" t="inlineStr">
@@ -23470,17 +23470,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -23489,10 +23489,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H43" t="n">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>TX3212501</t>
+          <t>TX0000157</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -23542,7 +23542,7 @@
         </is>
       </c>
       <c r="U43" s="2" t="n">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -23556,12 +23556,12 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>mchen@hotmail.com</t>
+          <t>mchen@example.com</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>500 Pacific Ave</t>
+          <t>810 Demo Street</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>***-**-1521</t>
+          <t>***-**-0101</t>
         </is>
       </c>
       <c r="BF43" s="2" t="n">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="CL43" t="inlineStr">
         <is>
-          <t>TX3261118</t>
+          <t>TX0000164</t>
         </is>
       </c>
       <c r="CM43" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="CR43" t="inlineStr">
         <is>
-          <t>(512) 621-2178</t>
+          <t>(512) 555-0100</t>
         </is>
       </c>
       <c r="CS43" t="inlineStr">
@@ -24005,17 +24005,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -24024,10 +24024,10 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H44" t="n">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>OH6635833</t>
+          <t>OH0000112</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -24077,7 +24077,7 @@
         </is>
       </c>
       <c r="U44" s="2" t="n">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -24091,12 +24091,12 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>sofiagomez@yahoo.com</t>
+          <t>sofiagomez@example.com</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>815 Prospect Ave</t>
+          <t>1020 Demo Street</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="BF44" s="2" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="CL44" t="inlineStr">
         <is>
-          <t>OH6635833</t>
+          <t>OH0000112</t>
         </is>
       </c>
       <c r="CM44" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="CR44" t="inlineStr">
         <is>
-          <t>(614) 574-7480</t>
+          <t>(614) 555-0105</t>
         </is>
       </c>
       <c r="CS44" t="inlineStr">
@@ -24532,17 +24532,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -24551,10 +24551,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H45" t="n">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>OH6094308</t>
+          <t>OH0000103</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -24604,7 +24604,7 @@
         </is>
       </c>
       <c r="U45" s="2" t="n">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -24618,12 +24618,12 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>sofiagomez@yahoo.com</t>
+          <t>sofiagomez@example.com</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>815 Prospect Ave</t>
+          <t>1020 Demo Street</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="BF45" s="2" t="n">
@@ -24851,7 +24851,7 @@
       </c>
       <c r="CL45" t="inlineStr">
         <is>
-          <t>OH6635834</t>
+          <t>OH0000113</t>
         </is>
       </c>
       <c r="CM45" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="CR45" t="inlineStr">
         <is>
-          <t>(614) 574-7480</t>
+          <t>(614) 555-0105</t>
         </is>
       </c>
       <c r="CS45" t="inlineStr">
@@ -25059,17 +25059,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -25078,10 +25078,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H46" t="n">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>OH5247055</t>
+          <t>OH0000101</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -25131,7 +25131,7 @@
         </is>
       </c>
       <c r="U46" s="2" t="n">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -25145,12 +25145,12 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>sofiagomez@yahoo.com</t>
+          <t>sofiagomez@example.com</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>815 Prospect Ave</t>
+          <t>1020 Demo Street</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -25259,7 +25259,7 @@
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="BF46" s="2" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="CL46" t="inlineStr">
         <is>
-          <t>OH6635835</t>
+          <t>OH0000114</t>
         </is>
       </c>
       <c r="CM46" t="inlineStr">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="CR46" t="inlineStr">
         <is>
-          <t>(614) 574-7480</t>
+          <t>(614) 555-0105</t>
         </is>
       </c>
       <c r="CS46" t="inlineStr">
@@ -25586,17 +25586,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -25605,10 +25605,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H47" t="n">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>OH8453480</t>
+          <t>OH0000129</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -25658,7 +25658,7 @@
         </is>
       </c>
       <c r="U47" s="2" t="n">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -25672,12 +25672,12 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>sofiagomez@yahoo.com</t>
+          <t>sofiagomez@example.com</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>815 Prospect Ave</t>
+          <t>1020 Demo Street</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -25786,7 +25786,7 @@
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="BF47" s="2" t="n">
@@ -25905,7 +25905,7 @@
       </c>
       <c r="CL47" t="inlineStr">
         <is>
-          <t>OH6635836</t>
+          <t>OH0000115</t>
         </is>
       </c>
       <c r="CM47" t="inlineStr">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="CR47" t="inlineStr">
         <is>
-          <t>(614) 574-7480</t>
+          <t>(614) 555-0105</t>
         </is>
       </c>
       <c r="CS47" t="inlineStr">
@@ -26113,17 +26113,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -26132,10 +26132,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H48" t="n">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>OH6843221</t>
+          <t>OH0000120</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="U48" s="2" t="n">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -26199,12 +26199,12 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>sofiagomez@yahoo.com</t>
+          <t>sofiagomez@example.com</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>815 Prospect Ave</t>
+          <t>1020 Demo Street</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="BF48" s="2" t="n">
@@ -26432,7 +26432,7 @@
       </c>
       <c r="CL48" t="inlineStr">
         <is>
-          <t>OH6635837</t>
+          <t>OH0000116</t>
         </is>
       </c>
       <c r="CM48" t="inlineStr">
@@ -26458,7 +26458,7 @@
       </c>
       <c r="CR48" t="inlineStr">
         <is>
-          <t>(614) 574-7480</t>
+          <t>(614) 555-0105</t>
         </is>
       </c>
       <c r="CS48" t="inlineStr">
@@ -26640,17 +26640,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -26659,10 +26659,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H49" t="n">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>OH6877493</t>
+          <t>OH0000121</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -26717,7 +26717,7 @@
         </is>
       </c>
       <c r="U49" s="2" t="n">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -26731,12 +26731,12 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>sofiagomez@yahoo.com</t>
+          <t>sofiagomez@example.com</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>815 Prospect Ave</t>
+          <t>1020 Demo Street</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="BF49" s="2" t="n">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="CL49" t="inlineStr">
         <is>
-          <t>OH6635838</t>
+          <t>OH0000117</t>
         </is>
       </c>
       <c r="CM49" t="inlineStr">
@@ -26990,7 +26990,7 @@
       </c>
       <c r="CR49" t="inlineStr">
         <is>
-          <t>(614) 574-7480</t>
+          <t>(614) 555-0105</t>
         </is>
       </c>
       <c r="CS49" t="inlineStr">
@@ -27172,17 +27172,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -27191,10 +27191,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H50" t="n">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>OH1110710</t>
+          <t>OH0000073</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -27244,7 +27244,7 @@
         </is>
       </c>
       <c r="U50" s="2" t="n">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -27258,12 +27258,12 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>sofiagomez@yahoo.com</t>
+          <t>sofiagomez@example.com</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>815 Prospect Ave</t>
+          <t>1020 Demo Street</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -27372,7 +27372,7 @@
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>***-**-4815</t>
+          <t>***-**-0109</t>
         </is>
       </c>
       <c r="BF50" s="2" t="n">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="CL50" t="inlineStr">
         <is>
-          <t>OH6635839</t>
+          <t>OH0000118</t>
         </is>
       </c>
       <c r="CM50" t="inlineStr">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="CR50" t="inlineStr">
         <is>
-          <t>(614) 574-7480</t>
+          <t>(614) 555-0105</t>
         </is>
       </c>
       <c r="CS50" t="inlineStr">
@@ -27699,17 +27699,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -27718,10 +27718,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H51" t="n">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>OH9450480</t>
+          <t>OH0000141</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -27771,7 +27771,7 @@
         </is>
       </c>
       <c r="U51" s="2" t="n">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -27785,12 +27785,12 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>liamsmith@gmail.com</t>
+          <t>liamsmith@example.com</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>240 Madison Ave</t>
+          <t>530 Demo Street</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="BF51" s="2" t="n">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="CL51" t="inlineStr">
         <is>
-          <t>OH9450480</t>
+          <t>OH0000141</t>
         </is>
       </c>
       <c r="CM51" t="inlineStr">
@@ -28067,7 +28067,7 @@
       </c>
       <c r="CR51" t="inlineStr">
         <is>
-          <t>(614) 937-6329</t>
+          <t>(614) 555-0114</t>
         </is>
       </c>
       <c r="CS51" t="inlineStr">
@@ -28249,17 +28249,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -28268,10 +28268,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H52" t="n">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>OH8889985</t>
+          <t>OH0000139</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -28321,7 +28321,7 @@
         </is>
       </c>
       <c r="U52" s="2" t="n">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -28335,12 +28335,12 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>liamsmith@gmail.com</t>
+          <t>liamsmith@example.com</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>240 Madison Ave</t>
+          <t>530 Demo Street</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -28464,7 +28464,7 @@
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="BF52" s="2" t="n">
@@ -28591,7 +28591,7 @@
       </c>
       <c r="CL52" t="inlineStr">
         <is>
-          <t>OH9450481</t>
+          <t>OH0000142</t>
         </is>
       </c>
       <c r="CM52" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="CR52" t="inlineStr">
         <is>
-          <t>(614) 937-6329</t>
+          <t>(614) 555-0114</t>
         </is>
       </c>
       <c r="CS52" t="inlineStr">
@@ -28799,17 +28799,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -28818,10 +28818,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H53" t="n">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>OH2899009</t>
+          <t>OH0000091</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -28871,7 +28871,7 @@
         </is>
       </c>
       <c r="U53" s="2" t="n">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -28885,12 +28885,12 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>liamsmith@gmail.com</t>
+          <t>liamsmith@example.com</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>240 Madison Ave</t>
+          <t>530 Demo Street</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -29014,7 +29014,7 @@
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="BF53" s="2" t="n">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="CL53" t="inlineStr">
         <is>
-          <t>OH9450482</t>
+          <t>OH0000143</t>
         </is>
       </c>
       <c r="CM53" t="inlineStr">
@@ -29167,7 +29167,7 @@
       </c>
       <c r="CR53" t="inlineStr">
         <is>
-          <t>(614) 937-6329</t>
+          <t>(614) 555-0114</t>
         </is>
       </c>
       <c r="CS53" t="inlineStr">
@@ -29349,17 +29349,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -29368,10 +29368,10 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H54" t="n">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>OH8294998</t>
+          <t>OH0000128</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -29421,7 +29421,7 @@
         </is>
       </c>
       <c r="U54" s="2" t="n">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -29435,12 +29435,12 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>liamsmith@gmail.com</t>
+          <t>liamsmith@example.com</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>240 Madison Ave</t>
+          <t>530 Demo Street</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -29564,7 +29564,7 @@
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="BF54" s="2" t="n">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="CL54" t="inlineStr">
         <is>
-          <t>OH9450483</t>
+          <t>OH0000144</t>
         </is>
       </c>
       <c r="CM54" t="inlineStr">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="CR54" t="inlineStr">
         <is>
-          <t>(614) 937-6329</t>
+          <t>(614) 555-0114</t>
         </is>
       </c>
       <c r="CS54" t="inlineStr">
@@ -29899,17 +29899,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -29918,10 +29918,10 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H55" t="n">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>OH3539286</t>
+          <t>OH0000094</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="U55" s="2" t="n">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -29985,12 +29985,12 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>liamsmith@gmail.com</t>
+          <t>liamsmith@example.com</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>240 Madison Ave</t>
+          <t>530 Demo Street</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="BF55" s="2" t="n">
@@ -30241,7 +30241,7 @@
       </c>
       <c r="CL55" t="inlineStr">
         <is>
-          <t>OH9450484</t>
+          <t>OH0000145</t>
         </is>
       </c>
       <c r="CM55" t="inlineStr">
@@ -30267,7 +30267,7 @@
       </c>
       <c r="CR55" t="inlineStr">
         <is>
-          <t>(614) 937-6329</t>
+          <t>(614) 555-0114</t>
         </is>
       </c>
       <c r="CS55" t="inlineStr">
@@ -30449,17 +30449,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -30468,10 +30468,10 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H56" t="n">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>OH4520738</t>
+          <t>OH0000098</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -30526,7 +30526,7 @@
         </is>
       </c>
       <c r="U56" s="2" t="n">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -30540,12 +30540,12 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>liamsmith@gmail.com</t>
+          <t>liamsmith@example.com</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>240 Madison Ave</t>
+          <t>530 Demo Street</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -30669,7 +30669,7 @@
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="BF56" s="2" t="n">
@@ -30796,7 +30796,7 @@
       </c>
       <c r="CL56" t="inlineStr">
         <is>
-          <t>OH9450485</t>
+          <t>OH0000146</t>
         </is>
       </c>
       <c r="CM56" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="CR56" t="inlineStr">
         <is>
-          <t>(614) 937-6329</t>
+          <t>(614) 555-0114</t>
         </is>
       </c>
       <c r="CS56" t="inlineStr">
@@ -31004,17 +31004,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H57" t="n">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>OH9851872</t>
+          <t>OH0000150</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -31076,7 +31076,7 @@
         </is>
       </c>
       <c r="U57" s="2" t="n">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -31090,12 +31090,12 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>liamsmith@gmail.com</t>
+          <t>liamsmith@example.com</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>240 Madison Ave</t>
+          <t>530 Demo Street</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>***-**-4800</t>
+          <t>***-**-0108</t>
         </is>
       </c>
       <c r="BF57" s="2" t="n">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="CL57" t="inlineStr">
         <is>
-          <t>OH9450486</t>
+          <t>OH0000147</t>
         </is>
       </c>
       <c r="CM57" t="inlineStr">
@@ -31372,7 +31372,7 @@
       </c>
       <c r="CR57" t="inlineStr">
         <is>
-          <t>(614) 937-6329</t>
+          <t>(614) 555-0114</t>
         </is>
       </c>
       <c r="CS57" t="inlineStr">
@@ -31554,17 +31554,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -31573,10 +31573,10 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H58" t="n">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>OH6116714</t>
+          <t>OH0000104</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="U58" s="2" t="n">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -31640,12 +31640,12 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>emmabrown@yahoo.com</t>
+          <t>emmabrown@example.com</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr</t>
+          <t>630 Demo Street</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -31764,7 +31764,7 @@
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="BF58" s="2" t="n">
@@ -31888,7 +31888,7 @@
       </c>
       <c r="CL58" t="inlineStr">
         <is>
-          <t>OH6116714</t>
+          <t>OH0000104</t>
         </is>
       </c>
       <c r="CM58" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="CR58" t="inlineStr">
         <is>
-          <t>(614) 935-8132</t>
+          <t>(614) 555-0113</t>
         </is>
       </c>
       <c r="CS58" t="inlineStr">
@@ -32096,17 +32096,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -32115,10 +32115,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H59" t="n">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>OH2742151</t>
+          <t>OH0000083</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -32168,7 +32168,7 @@
         </is>
       </c>
       <c r="U59" s="2" t="n">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -32182,12 +32182,12 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>emmabrown@yahoo.com</t>
+          <t>emmabrown@example.com</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr</t>
+          <t>630 Demo Street</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -32306,7 +32306,7 @@
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="BF59" s="2" t="n">
@@ -32430,7 +32430,7 @@
       </c>
       <c r="CL59" t="inlineStr">
         <is>
-          <t>OH6116715</t>
+          <t>OH0000105</t>
         </is>
       </c>
       <c r="CM59" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="CR59" t="inlineStr">
         <is>
-          <t>(614) 935-8132</t>
+          <t>(614) 555-0113</t>
         </is>
       </c>
       <c r="CS59" t="inlineStr">
@@ -32638,17 +32638,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -32657,10 +32657,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H60" t="n">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>OH5031927</t>
+          <t>OH0000100</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -32710,7 +32710,7 @@
         </is>
       </c>
       <c r="U60" s="2" t="n">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -32724,12 +32724,12 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>emmabrown@yahoo.com</t>
+          <t>emmabrown@example.com</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr</t>
+          <t>630 Demo Street</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -32848,7 +32848,7 @@
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="BF60" s="2" t="n">
@@ -32972,7 +32972,7 @@
       </c>
       <c r="CL60" t="inlineStr">
         <is>
-          <t>OH6116716</t>
+          <t>OH0000106</t>
         </is>
       </c>
       <c r="CM60" t="inlineStr">
@@ -32998,7 +32998,7 @@
       </c>
       <c r="CR60" t="inlineStr">
         <is>
-          <t>(614) 935-8132</t>
+          <t>(614) 555-0113</t>
         </is>
       </c>
       <c r="CS60" t="inlineStr">
@@ -33180,17 +33180,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -33199,10 +33199,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H61" t="n">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>OH9570143</t>
+          <t>OH0000148</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="U61" s="2" t="n">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -33266,12 +33266,12 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>emmabrown@yahoo.com</t>
+          <t>emmabrown@example.com</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr</t>
+          <t>630 Demo Street</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -33390,7 +33390,7 @@
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="BF61" s="2" t="n">
@@ -33514,7 +33514,7 @@
       </c>
       <c r="CL61" t="inlineStr">
         <is>
-          <t>OH6116717</t>
+          <t>OH0000107</t>
         </is>
       </c>
       <c r="CM61" t="inlineStr">
@@ -33540,7 +33540,7 @@
       </c>
       <c r="CR61" t="inlineStr">
         <is>
-          <t>(614) 935-8132</t>
+          <t>(614) 555-0113</t>
         </is>
       </c>
       <c r="CS61" t="inlineStr">
@@ -33722,17 +33722,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -33741,10 +33741,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H62" t="n">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>OH7265424</t>
+          <t>OH0000122</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="U62" s="2" t="n">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -33808,12 +33808,12 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>emmabrown@yahoo.com</t>
+          <t>emmabrown@example.com</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr</t>
+          <t>630 Demo Street</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -33932,7 +33932,7 @@
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="BF62" s="2" t="n">
@@ -34056,7 +34056,7 @@
       </c>
       <c r="CL62" t="inlineStr">
         <is>
-          <t>OH6116718</t>
+          <t>OH0000108</t>
         </is>
       </c>
       <c r="CM62" t="inlineStr">
@@ -34082,7 +34082,7 @@
       </c>
       <c r="CR62" t="inlineStr">
         <is>
-          <t>(614) 935-8132</t>
+          <t>(614) 555-0113</t>
         </is>
       </c>
       <c r="CS62" t="inlineStr">
@@ -34264,17 +34264,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H63" t="n">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>OH4179820</t>
+          <t>OH0000096</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
@@ -34341,7 +34341,7 @@
         </is>
       </c>
       <c r="U63" s="2" t="n">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -34355,12 +34355,12 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>emmabrown@yahoo.com</t>
+          <t>emmabrown@example.com</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr</t>
+          <t>630 Demo Street</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -34479,7 +34479,7 @@
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="BF63" s="2" t="n">
@@ -34603,7 +34603,7 @@
       </c>
       <c r="CL63" t="inlineStr">
         <is>
-          <t>OH6116719</t>
+          <t>OH0000109</t>
         </is>
       </c>
       <c r="CM63" t="inlineStr">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="CR63" t="inlineStr">
         <is>
-          <t>(614) 935-8132</t>
+          <t>(614) 555-0113</t>
         </is>
       </c>
       <c r="CS63" t="inlineStr">
@@ -34811,17 +34811,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -34830,10 +34830,10 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H64" t="n">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>OH9306784</t>
+          <t>OH0000140</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -34883,7 +34883,7 @@
         </is>
       </c>
       <c r="U64" s="2" t="n">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -34897,12 +34897,12 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>emmabrown@yahoo.com</t>
+          <t>emmabrown@example.com</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr</t>
+          <t>630 Demo Street</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -35021,7 +35021,7 @@
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>***-**-9930</t>
+          <t>***-**-0124</t>
         </is>
       </c>
       <c r="BF64" s="2" t="n">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="CL64" t="inlineStr">
         <is>
-          <t>OH6116720</t>
+          <t>OH0000110</t>
         </is>
       </c>
       <c r="CM64" t="inlineStr">
@@ -35171,7 +35171,7 @@
       </c>
       <c r="CR64" t="inlineStr">
         <is>
-          <t>(614) 935-8132</t>
+          <t>(614) 555-0113</t>
         </is>
       </c>
       <c r="CS64" t="inlineStr">
@@ -35353,17 +35353,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -35372,10 +35372,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H65" t="n">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>IL3858215</t>
+          <t>IL0000049</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -35425,7 +35425,7 @@
         </is>
       </c>
       <c r="U65" s="2" t="n">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -35439,12 +35439,12 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>nwilson@gmail.com</t>
+          <t>nwilson@example.com</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>110 W Adams St</t>
+          <t>130 Demo Street</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -35553,7 +35553,7 @@
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="BF65" s="2" t="n">
@@ -35675,7 +35675,7 @@
       </c>
       <c r="CL65" t="inlineStr">
         <is>
-          <t>IL3858215</t>
+          <t>IL0000049</t>
         </is>
       </c>
       <c r="CM65" t="inlineStr">
@@ -35701,7 +35701,7 @@
       </c>
       <c r="CR65" t="inlineStr">
         <is>
-          <t>(312) 807-8788</t>
+          <t>(312) 555-0109</t>
         </is>
       </c>
       <c r="CS65" t="inlineStr">
@@ -35883,17 +35883,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -35902,10 +35902,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H66" t="n">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>IL2016981</t>
+          <t>IL0000037</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -35955,7 +35955,7 @@
         </is>
       </c>
       <c r="U66" s="2" t="n">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -35969,12 +35969,12 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>nwilson@gmail.com</t>
+          <t>nwilson@example.com</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>110 W Adams St</t>
+          <t>130 Demo Street</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -36083,7 +36083,7 @@
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="BF66" s="2" t="n">
@@ -36205,7 +36205,7 @@
       </c>
       <c r="CL66" t="inlineStr">
         <is>
-          <t>IL3858216</t>
+          <t>IL0000050</t>
         </is>
       </c>
       <c r="CM66" t="inlineStr">
@@ -36231,7 +36231,7 @@
       </c>
       <c r="CR66" t="inlineStr">
         <is>
-          <t>(312) 807-8788</t>
+          <t>(312) 555-0109</t>
         </is>
       </c>
       <c r="CS66" t="inlineStr">
@@ -36413,17 +36413,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -36432,10 +36432,10 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H67" t="n">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>IL4814730</t>
+          <t>IL0000060</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -36485,7 +36485,7 @@
         </is>
       </c>
       <c r="U67" s="2" t="n">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -36499,12 +36499,12 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>nwilson@gmail.com</t>
+          <t>nwilson@example.com</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>110 W Adams St</t>
+          <t>130 Demo Street</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -36613,7 +36613,7 @@
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="BF67" s="2" t="n">
@@ -36735,7 +36735,7 @@
       </c>
       <c r="CL67" t="inlineStr">
         <is>
-          <t>IL3858217</t>
+          <t>IL0000051</t>
         </is>
       </c>
       <c r="CM67" t="inlineStr">
@@ -36761,7 +36761,7 @@
       </c>
       <c r="CR67" t="inlineStr">
         <is>
-          <t>(312) 807-8788</t>
+          <t>(312) 555-0109</t>
         </is>
       </c>
       <c r="CS67" t="inlineStr">
@@ -36943,17 +36943,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -36962,10 +36962,10 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H68" t="n">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>IL4355788</t>
+          <t>IL0000059</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -37015,7 +37015,7 @@
         </is>
       </c>
       <c r="U68" s="2" t="n">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -37029,12 +37029,12 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>nwilson@gmail.com</t>
+          <t>nwilson@example.com</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>110 W Adams St</t>
+          <t>130 Demo Street</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -37143,7 +37143,7 @@
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="BF68" s="2" t="n">
@@ -37265,7 +37265,7 @@
       </c>
       <c r="CL68" t="inlineStr">
         <is>
-          <t>IL3858218</t>
+          <t>IL0000052</t>
         </is>
       </c>
       <c r="CM68" t="inlineStr">
@@ -37291,7 +37291,7 @@
       </c>
       <c r="CR68" t="inlineStr">
         <is>
-          <t>(312) 807-8788</t>
+          <t>(312) 555-0109</t>
         </is>
       </c>
       <c r="CS68" t="inlineStr">
@@ -37473,17 +37473,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -37492,10 +37492,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H69" t="n">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>IL6567205</t>
+          <t>IL0000064</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -37545,7 +37545,7 @@
         </is>
       </c>
       <c r="U69" s="2" t="n">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -37559,12 +37559,12 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>nwilson@gmail.com</t>
+          <t>nwilson@example.com</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>110 W Adams St</t>
+          <t>130 Demo Street</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -37673,7 +37673,7 @@
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="BF69" s="2" t="n">
@@ -37795,7 +37795,7 @@
       </c>
       <c r="CL69" t="inlineStr">
         <is>
-          <t>IL3858219</t>
+          <t>IL0000053</t>
         </is>
       </c>
       <c r="CM69" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="CR69" t="inlineStr">
         <is>
-          <t>(312) 807-8788</t>
+          <t>(312) 555-0109</t>
         </is>
       </c>
       <c r="CS69" t="inlineStr">
@@ -38003,17 +38003,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -38022,10 +38022,10 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H70" t="n">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>IL6135045</t>
+          <t>IL0000063</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -38080,7 +38080,7 @@
         </is>
       </c>
       <c r="U70" s="2" t="n">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -38094,12 +38094,12 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>nwilson@gmail.com</t>
+          <t>nwilson@example.com</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>110 W Adams St</t>
+          <t>130 Demo Street</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -38208,7 +38208,7 @@
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="BF70" s="2" t="n">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="CL70" t="inlineStr">
         <is>
-          <t>IL3858220</t>
+          <t>IL0000054</t>
         </is>
       </c>
       <c r="CM70" t="inlineStr">
@@ -38356,7 +38356,7 @@
       </c>
       <c r="CR70" t="inlineStr">
         <is>
-          <t>(312) 807-8788</t>
+          <t>(312) 555-0109</t>
         </is>
       </c>
       <c r="CS70" t="inlineStr">
@@ -38538,17 +38538,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -38557,10 +38557,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H71" t="n">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>IL2535912</t>
+          <t>IL0000038</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -38610,7 +38610,7 @@
         </is>
       </c>
       <c r="U71" s="2" t="n">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -38624,12 +38624,12 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>nwilson@gmail.com</t>
+          <t>nwilson@example.com</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>110 W Adams St</t>
+          <t>130 Demo Street</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -38738,7 +38738,7 @@
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>***-**-5590</t>
+          <t>***-**-0112</t>
         </is>
       </c>
       <c r="BF71" s="2" t="n">
@@ -38860,7 +38860,7 @@
       </c>
       <c r="CL71" t="inlineStr">
         <is>
-          <t>IL3858221</t>
+          <t>IL0000055</t>
         </is>
       </c>
       <c r="CM71" t="inlineStr">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="CR71" t="inlineStr">
         <is>
-          <t>(312) 807-8788</t>
+          <t>(312) 555-0109</t>
         </is>
       </c>
       <c r="CS71" t="inlineStr">
@@ -39068,17 +39068,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -39087,10 +39087,10 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H72" t="n">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>GA8190601</t>
+          <t>GA0000020</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -39140,7 +39140,7 @@
         </is>
       </c>
       <c r="U72" s="2" t="n">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -39154,12 +39154,12 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>olee@hotmail.com</t>
+          <t>olee@example.com</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>600 Peachtree St</t>
+          <t>900 Demo Street</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -39268,7 +39268,7 @@
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="BF72" s="2" t="n">
@@ -39390,7 +39390,7 @@
       </c>
       <c r="CL72" t="inlineStr">
         <is>
-          <t>GA8190601</t>
+          <t>GA0000020</t>
         </is>
       </c>
       <c r="CM72" t="inlineStr">
@@ -39416,7 +39416,7 @@
       </c>
       <c r="CR72" t="inlineStr">
         <is>
-          <t>(404) 231-4428</t>
+          <t>(404) 555-0100</t>
         </is>
       </c>
       <c r="CS72" t="inlineStr">
@@ -39598,17 +39598,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -39617,10 +39617,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H73" t="n">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>GA4750278</t>
+          <t>GA0000007</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -39670,7 +39670,7 @@
         </is>
       </c>
       <c r="U73" s="2" t="n">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -39684,12 +39684,12 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>olee@hotmail.com</t>
+          <t>olee@example.com</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>600 Peachtree St</t>
+          <t>900 Demo Street</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
@@ -39798,7 +39798,7 @@
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="BF73" s="2" t="n">
@@ -39920,7 +39920,7 @@
       </c>
       <c r="CL73" t="inlineStr">
         <is>
-          <t>GA8190602</t>
+          <t>GA0000021</t>
         </is>
       </c>
       <c r="CM73" t="inlineStr">
@@ -39946,7 +39946,7 @@
       </c>
       <c r="CR73" t="inlineStr">
         <is>
-          <t>(404) 231-4428</t>
+          <t>(404) 555-0100</t>
         </is>
       </c>
       <c r="CS73" t="inlineStr">
@@ -40128,17 +40128,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -40147,10 +40147,10 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H74" t="n">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>GA5818610</t>
+          <t>GA0000009</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -40200,7 +40200,7 @@
         </is>
       </c>
       <c r="U74" s="2" t="n">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -40214,12 +40214,12 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>olee@hotmail.com</t>
+          <t>olee@example.com</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>600 Peachtree St</t>
+          <t>900 Demo Street</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
@@ -40328,7 +40328,7 @@
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="BF74" s="2" t="n">
@@ -40450,7 +40450,7 @@
       </c>
       <c r="CL74" t="inlineStr">
         <is>
-          <t>GA8190603</t>
+          <t>GA0000022</t>
         </is>
       </c>
       <c r="CM74" t="inlineStr">
@@ -40476,7 +40476,7 @@
       </c>
       <c r="CR74" t="inlineStr">
         <is>
-          <t>(404) 231-4428</t>
+          <t>(404) 555-0100</t>
         </is>
       </c>
       <c r="CS74" t="inlineStr">
@@ -40658,17 +40658,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -40677,10 +40677,10 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H75" t="n">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>GA5852321</t>
+          <t>GA0000010</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -40730,7 +40730,7 @@
         </is>
       </c>
       <c r="U75" s="2" t="n">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -40744,12 +40744,12 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>olee@hotmail.com</t>
+          <t>olee@example.com</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>600 Peachtree St</t>
+          <t>900 Demo Street</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -40858,7 +40858,7 @@
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="BF75" s="2" t="n">
@@ -40980,7 +40980,7 @@
       </c>
       <c r="CL75" t="inlineStr">
         <is>
-          <t>GA8190604</t>
+          <t>GA0000023</t>
         </is>
       </c>
       <c r="CM75" t="inlineStr">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="CR75" t="inlineStr">
         <is>
-          <t>(404) 231-4428</t>
+          <t>(404) 555-0100</t>
         </is>
       </c>
       <c r="CS75" t="inlineStr">
@@ -41188,17 +41188,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -41207,10 +41207,10 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H76" t="n">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>GA6447082</t>
+          <t>GA0000012</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="U76" s="2" t="n">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -41274,12 +41274,12 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>olee@hotmail.com</t>
+          <t>olee@example.com</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>600 Peachtree St</t>
+          <t>900 Demo Street</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
@@ -41388,7 +41388,7 @@
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="BF76" s="2" t="n">
@@ -41510,7 +41510,7 @@
       </c>
       <c r="CL76" t="inlineStr">
         <is>
-          <t>GA8190605</t>
+          <t>GA0000024</t>
         </is>
       </c>
       <c r="CM76" t="inlineStr">
@@ -41536,7 +41536,7 @@
       </c>
       <c r="CR76" t="inlineStr">
         <is>
-          <t>(404) 231-4428</t>
+          <t>(404) 555-0100</t>
         </is>
       </c>
       <c r="CS76" t="inlineStr">
@@ -41718,17 +41718,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -41737,10 +41737,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H77" t="n">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>GA5384195</t>
+          <t>GA0000008</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -41795,7 +41795,7 @@
         </is>
       </c>
       <c r="U77" s="2" t="n">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -41809,12 +41809,12 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>olee@hotmail.com</t>
+          <t>olee@example.com</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>600 Peachtree St</t>
+          <t>900 Demo Street</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -41923,7 +41923,7 @@
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="BF77" s="2" t="n">
@@ -42045,7 +42045,7 @@
       </c>
       <c r="CL77" t="inlineStr">
         <is>
-          <t>GA8190606</t>
+          <t>GA0000025</t>
         </is>
       </c>
       <c r="CM77" t="inlineStr">
@@ -42071,7 +42071,7 @@
       </c>
       <c r="CR77" t="inlineStr">
         <is>
-          <t>(404) 231-4428</t>
+          <t>(404) 555-0100</t>
         </is>
       </c>
       <c r="CS77" t="inlineStr">
@@ -42253,17 +42253,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -42272,10 +42272,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H78" t="n">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>GA1861689</t>
+          <t>GA0000003</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -42325,7 +42325,7 @@
         </is>
       </c>
       <c r="U78" s="2" t="n">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -42339,12 +42339,12 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>olee@hotmail.com</t>
+          <t>olee@example.com</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>600 Peachtree St</t>
+          <t>900 Demo Street</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
@@ -42453,7 +42453,7 @@
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>***-**-5273</t>
+          <t>***-**-0111</t>
         </is>
       </c>
       <c r="BF78" s="2" t="n">
@@ -42575,7 +42575,7 @@
       </c>
       <c r="CL78" t="inlineStr">
         <is>
-          <t>GA8190607</t>
+          <t>GA0000026</t>
         </is>
       </c>
       <c r="CM78" t="inlineStr">
@@ -42601,7 +42601,7 @@
       </c>
       <c r="CR78" t="inlineStr">
         <is>
-          <t>(404) 231-4428</t>
+          <t>(404) 555-0100</t>
         </is>
       </c>
       <c r="CS78" t="inlineStr">
@@ -42783,17 +42783,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave, Chicago, IL 60605</t>
+          <t>920 Demo Street, Chicago, IL 60605</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>618-667-2121</t>
+          <t>618-555-0101</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -42802,10 +42802,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H79" t="n">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>IL1895570</t>
+          <t>IL0000030</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -42855,7 +42855,7 @@
         </is>
       </c>
       <c r="U79" s="2" t="n">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -42869,12 +42869,12 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>robertjohnson@hotmail.com</t>
+          <t>robertjohnson@example.com</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave</t>
+          <t>920 Demo Street</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
@@ -42993,7 +42993,7 @@
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="BF79" s="2" t="n">
@@ -43120,7 +43120,7 @@
       </c>
       <c r="CL79" t="inlineStr">
         <is>
-          <t>IL1895570</t>
+          <t>IL0000030</t>
         </is>
       </c>
       <c r="CM79" t="inlineStr">
@@ -43146,7 +43146,7 @@
       </c>
       <c r="CR79" t="inlineStr">
         <is>
-          <t>(312) 300-1431</t>
+          <t>(312) 555-0103</t>
         </is>
       </c>
       <c r="CS79" t="inlineStr">
@@ -43328,17 +43328,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave, Chicago, IL 60605</t>
+          <t>920 Demo Street, Chicago, IL 60605</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>618-667-2121</t>
+          <t>618-555-0101</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -43347,10 +43347,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H80" t="n">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>IL5451183</t>
+          <t>IL0000062</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -43400,7 +43400,7 @@
         </is>
       </c>
       <c r="U80" s="2" t="n">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -43414,12 +43414,12 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>robertjohnson@hotmail.com</t>
+          <t>robertjohnson@example.com</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave</t>
+          <t>920 Demo Street</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
@@ -43538,7 +43538,7 @@
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="BF80" s="2" t="n">
@@ -43665,7 +43665,7 @@
       </c>
       <c r="CL80" t="inlineStr">
         <is>
-          <t>IL1895571</t>
+          <t>IL0000031</t>
         </is>
       </c>
       <c r="CM80" t="inlineStr">
@@ -43691,7 +43691,7 @@
       </c>
       <c r="CR80" t="inlineStr">
         <is>
-          <t>(312) 300-1431</t>
+          <t>(312) 555-0103</t>
         </is>
       </c>
       <c r="CS80" t="inlineStr">
@@ -43873,17 +43873,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave, Chicago, IL 60605</t>
+          <t>920 Demo Street, Chicago, IL 60605</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>618-667-2121</t>
+          <t>618-555-0101</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -43892,10 +43892,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H81" t="n">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>IL2852329</t>
+          <t>IL0000040</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -43945,7 +43945,7 @@
         </is>
       </c>
       <c r="U81" s="2" t="n">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -43959,12 +43959,12 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>robertjohnson@hotmail.com</t>
+          <t>robertjohnson@example.com</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave</t>
+          <t>920 Demo Street</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
@@ -44083,7 +44083,7 @@
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="BF81" s="2" t="n">
@@ -44210,7 +44210,7 @@
       </c>
       <c r="CL81" t="inlineStr">
         <is>
-          <t>IL1895572</t>
+          <t>IL0000032</t>
         </is>
       </c>
       <c r="CM81" t="inlineStr">
@@ -44236,7 +44236,7 @@
       </c>
       <c r="CR81" t="inlineStr">
         <is>
-          <t>(312) 300-1431</t>
+          <t>(312) 555-0103</t>
         </is>
       </c>
       <c r="CS81" t="inlineStr">
@@ -44418,17 +44418,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave, Chicago, IL 60605</t>
+          <t>920 Demo Street, Chicago, IL 60605</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>618-667-2121</t>
+          <t>618-555-0101</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -44437,10 +44437,10 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H82" t="n">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>IL4305571</t>
+          <t>IL0000057</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -44490,7 +44490,7 @@
         </is>
       </c>
       <c r="U82" s="2" t="n">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -44504,12 +44504,12 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>robertjohnson@hotmail.com</t>
+          <t>robertjohnson@example.com</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave</t>
+          <t>920 Demo Street</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
@@ -44628,7 +44628,7 @@
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="BF82" s="2" t="n">
@@ -44755,7 +44755,7 @@
       </c>
       <c r="CL82" t="inlineStr">
         <is>
-          <t>IL1895573</t>
+          <t>IL0000033</t>
         </is>
       </c>
       <c r="CM82" t="inlineStr">
@@ -44781,7 +44781,7 @@
       </c>
       <c r="CR82" t="inlineStr">
         <is>
-          <t>(312) 300-1431</t>
+          <t>(312) 555-0103</t>
         </is>
       </c>
       <c r="CS82" t="inlineStr">
@@ -44963,17 +44963,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave, Chicago, IL 60605</t>
+          <t>920 Demo Street, Chicago, IL 60605</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>618-667-2121</t>
+          <t>618-555-0101</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -44982,10 +44982,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H83" t="n">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>IL8325086</t>
+          <t>IL0000066</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -45035,7 +45035,7 @@
         </is>
       </c>
       <c r="U83" s="2" t="n">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -45049,12 +45049,12 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>robertjohnson@hotmail.com</t>
+          <t>robertjohnson@example.com</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave</t>
+          <t>920 Demo Street</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
@@ -45173,7 +45173,7 @@
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="BF83" s="2" t="n">
@@ -45300,7 +45300,7 @@
       </c>
       <c r="CL83" t="inlineStr">
         <is>
-          <t>IL1895574</t>
+          <t>IL0000034</t>
         </is>
       </c>
       <c r="CM83" t="inlineStr">
@@ -45326,7 +45326,7 @@
       </c>
       <c r="CR83" t="inlineStr">
         <is>
-          <t>(312) 300-1431</t>
+          <t>(312) 555-0103</t>
         </is>
       </c>
       <c r="CS83" t="inlineStr">
@@ -45508,17 +45508,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave, Chicago, IL 60605</t>
+          <t>920 Demo Street, Chicago, IL 60605</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>618-667-2121</t>
+          <t>618-555-0101</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -45527,10 +45527,10 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H84" t="n">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>IL3423206</t>
+          <t>IL0000048</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -45585,7 +45585,7 @@
         </is>
       </c>
       <c r="U84" s="2" t="n">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -45599,12 +45599,12 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>robertjohnson@hotmail.com</t>
+          <t>robertjohnson@example.com</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave</t>
+          <t>920 Demo Street</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
@@ -45723,7 +45723,7 @@
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="BF84" s="2" t="n">
@@ -45850,7 +45850,7 @@
       </c>
       <c r="CL84" t="inlineStr">
         <is>
-          <t>IL1895575</t>
+          <t>IL0000035</t>
         </is>
       </c>
       <c r="CM84" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="CR84" t="inlineStr">
         <is>
-          <t>(312) 300-1431</t>
+          <t>(312) 555-0103</t>
         </is>
       </c>
       <c r="CS84" t="inlineStr">
@@ -46058,17 +46058,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave, Chicago, IL 60605</t>
+          <t>920 Demo Street, Chicago, IL 60605</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>618-667-2121</t>
+          <t>618-555-0101</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -46077,10 +46077,10 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H85" t="n">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>IL2655126</t>
+          <t>IL0000039</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -46130,7 +46130,7 @@
         </is>
       </c>
       <c r="U85" s="2" t="n">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -46144,12 +46144,12 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>robertjohnson@hotmail.com</t>
+          <t>robertjohnson@example.com</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>618 S Michigan Ave</t>
+          <t>920 Demo Street</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
@@ -46268,7 +46268,7 @@
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>***-**-5664</t>
+          <t>***-**-0114</t>
         </is>
       </c>
       <c r="BF85" s="2" t="n">
@@ -46395,7 +46395,7 @@
       </c>
       <c r="CL85" t="inlineStr">
         <is>
-          <t>IL1895576</t>
+          <t>IL0000036</t>
         </is>
       </c>
       <c r="CM85" t="inlineStr">
@@ -46421,7 +46421,7 @@
       </c>
       <c r="CR85" t="inlineStr">
         <is>
-          <t>(312) 300-1431</t>
+          <t>(312) 555-0103</t>
         </is>
       </c>
       <c r="CS85" t="inlineStr">
